--- a/docs/perechen-otchetov/obrazcy/ФО-95.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-95.xlsx
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Строка детали — кредит: договор с валютой («№ … от …, KGS»), суммы, дата и способ погашения. В отчёт попадают кредиты, задолженность по которым (основная сумма + проценты + штрафы) стала нулевой в периоде платежом или принятием имущества в погашение; дата погашения — день, когда задолженность обнулилась. Списанные кредиты показывает ФО-11, перевод долга — ФО-12. Над кредитами разрезы, по умолчанию область → район → заёмщик; у городов республиканского значения — обе строки, области и района. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над его строками. Порядок: области — по справочнику (области по алфавиту, затем г. Бишкек, г. Ош); районы — по алфавиту; заёмщики — по алфавиту; кредиты заёмщика — по дате погашения. Суммы — в тыс. сом; валютный кредит: сумма по договору и получено — по курсу на конец периода, погашено — каждый платёж по курсу на день платежа, под кредитом строка «в тыс. &lt;валюта&gt; (курс …)».</t>
+          <t>Строка детали — кредит: договор с валютой («№ … от …, KGS»), суммы, дата и способ погашения. В отчёт попадают кредиты, задолженность по которым (основная сумма + проценты + штрафы) стала нулевой в периоде платежом или принятием имущества в погашение; дата погашения — день, когда задолженность обнулилась. Списанные кредиты показывает ФО-11, перевод долга — ФО-58. Над кредитами разрезы, по умолчанию область → район → заёмщик; у городов республиканского значения — обе строки, области и района. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над его строками. Порядок: области — по справочнику (области по алфавиту, затем г. Бишкек, г. Ош); районы — по алфавиту; заёмщики — по алфавиту; кредиты заёмщика — по дате погашения. Суммы — в тыс. сом; валютный кредит: сумма по договору и получено — по курсу на конец периода, погашено — каждый платёж по курсу на день платежа, под кредитом строка «в тыс. &lt;валюта&gt; (курс …)».</t>
         </is>
       </c>
     </row>
